--- a/新数据生成/关卡表/10030.xlsx
+++ b/新数据生成/关卡表/10030.xlsx
@@ -459,8 +459,8 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="13.2" customWidth="1" min="13" max="13"/>
     <col width="13.2" customWidth="1" min="14" max="14"/>
-    <col width="17.6" customWidth="1" min="15" max="15"/>
-    <col width="4.4" customWidth="1" min="16" max="16"/>
+    <col width="13.2" customWidth="1" min="15" max="15"/>
+    <col width="13.2" customWidth="1" min="16" max="16"/>
     <col width="4.4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -693,10 +693,14 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>角色平均等级</t>
-        </is>
-      </c>
-      <c r="P6" s="1" t="n"/>
+          <t>阵容强度</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>参考等级</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="n">
@@ -709,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>22.7</v>
+        <v>26.5</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -741,7 +745,10 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -752,23 +759,23 @@
         <v>2008</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>22.7</v>
+        <v>26.5</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -781,7 +788,10 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -795,10 +805,10 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="n">
-        <v>22.7</v>
+        <v>26.5</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
@@ -806,8 +816,9 @@
           <t>轻松</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>3</v>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -818,10 +829,10 @@
         <v>2002</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
@@ -831,10 +842,10 @@
         <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>19</v>
+        <v>17.4</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>8.1</v>
+        <v>5.1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -847,7 +858,10 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -858,23 +872,23 @@
         <v>2007</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>19</v>
+        <v>17.4</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8.1</v>
+        <v>5.1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -887,47 +901,37 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>2005</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="n">
-        <v>19</v>
+        <v>17.4</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>刘易斯</t>
-        </is>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>3</v>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -935,39 +939,42 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>21.1</v>
+        <v>15.3</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-8</v>
+        <v>-3.3</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -975,79 +982,69 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>21.1</v>
+        <v>15.3</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-8</v>
+        <v>-3.3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="n">
-        <v>21.1</v>
+        <v>15.3</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-3.3</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>3</v>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1071,10 +1068,10 @@
         <v>1.2</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>19.8</v>
+        <v>20.7</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1087,7 +1084,10 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1098,23 +1098,23 @@
         <v>2005</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>19.8</v>
+        <v>20.7</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1127,47 +1127,37 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="n">
-        <v>19.8</v>
+        <v>20.7</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>3</v>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1175,30 +1165,30 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>26.5</v>
+        <v>18.4</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-8.4</v>
+        <v>-4.9</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1207,7 +1197,10 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1215,30 +1208,30 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>26.5</v>
+        <v>18.4</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-8.4</v>
+        <v>-4.9</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1247,33 +1240,53 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K21" s="2" t="n">
-        <v>26.5</v>
+        <v>18.4</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+        <v>-4.9</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>泰森</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1284,23 +1297,23 @@
         <v>2002</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>22.2</v>
+        <v>18</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1313,7 +1326,10 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1321,30 +1337,30 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>22.2</v>
+        <v>18</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>垃圾刺客</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -1353,7 +1369,10 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1367,10 +1386,10 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="n">
-        <v>22.2</v>
+        <v>18</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
@@ -1378,8 +1397,9 @@
           <t>困难</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>3</v>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1387,39 +1407,42 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>10.1</v>
+        <v>26.7</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-3.9</v>
+        <v>-6.9</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1427,79 +1450,69 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J26" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K26" s="2" t="n">
-        <v>10.1</v>
+        <v>26.7</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-3.9</v>
+        <v>-6.9</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="D27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="n">
-        <v>10.1</v>
+        <v>26.7</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>残酷射手</t>
-        </is>
-      </c>
+        <v>-6.9</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>3</v>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1513,20 +1526,20 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>21.7</v>
+        <v>17.9</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -1539,7 +1552,10 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1550,23 +1566,23 @@
         <v>2006</v>
       </c>
       <c r="F29" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>21.7</v>
+        <v>17.9</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1595,10 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1590,23 +1609,23 @@
         <v>2007</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>21.7</v>
+        <v>17.9</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -1619,7 +1638,10 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1627,39 +1649,42 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2001</v>
+        <v>2008</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>13</v>
+        <v>22.9</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2.2</v>
+        <v>-3.6</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1667,39 +1692,42 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>13</v>
+        <v>22.9</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2.2</v>
+        <v>-3.6</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1713,19 +1741,20 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="n">
-        <v>13</v>
+        <v>22.9</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2.2</v>
+        <v>-3.6</v>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>3</v>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1733,79 +1762,89 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="F34" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>23.4</v>
+        <v>11.2</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>9.6</v>
+        <v>-6.9</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="D35" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>2004</v>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>3998</t>
+        </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>31626</v>
+      </c>
       <c r="I35" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>23.4</v>
+        <v>11.2</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>9.6</v>
+        <v>-6.9</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>技能Boss2</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1819,19 +1858,20 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="n">
-        <v>23.4</v>
+        <v>11.2</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>9.6</v>
+        <v>-6.9</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>3</v>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1839,30 +1879,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2001</v>
+        <v>2008</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-2.7</v>
+        <v>-1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -1871,7 +1911,10 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1882,23 +1925,23 @@
         <v>2003</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>-2.7</v>
+        <v>-1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -1911,7 +1954,10 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1919,30 +1965,30 @@
         <v>11</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-2.7</v>
+        <v>-1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -1951,7 +1997,10 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1962,23 +2011,23 @@
         <v>2002</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>17.3</v>
+        <v>17.9</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -1991,7 +2040,10 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1999,30 +2051,30 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>17.3</v>
+        <v>17.9</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>垃圾刺客</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2031,47 +2083,37 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="n">
-        <v>17.3</v>
+        <v>17.9</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O42" s="2" t="n">
-        <v>3</v>
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2079,30 +2121,30 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>14.3</v>
+        <v>23.9</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-7.4</v>
+        <v>-3.1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2111,7 +2153,10 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2119,13 +2164,13 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
@@ -2135,14 +2180,14 @@
         <v>1.1</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>14.3</v>
+        <v>23.9</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>-7.4</v>
+        <v>-3.1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2151,7 +2196,10 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2165,10 +2213,10 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="n">
-        <v>14.3</v>
+        <v>23.9</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>-7.4</v>
+        <v>-3.1</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
@@ -2176,8 +2224,9 @@
           <t>轻松</t>
         </is>
       </c>
-      <c r="O45" s="2" t="n">
-        <v>3</v>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2185,39 +2234,42 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>15.1</v>
+        <v>12.7</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2225,39 +2277,42 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>15.1</v>
+        <v>12.7</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2265,39 +2320,42 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>15.1</v>
+        <v>12.7</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2305,39 +2363,42 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>21.5</v>
+        <v>18.7</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>-4</v>
+        <v>5.5</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2345,39 +2406,42 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>21.5</v>
+        <v>18.7</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>-4</v>
+        <v>5.5</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2391,19 +2455,20 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="n">
-        <v>21.5</v>
+        <v>18.7</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>-4</v>
+        <v>5.5</v>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>3</v>
+          <t>地狱</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2411,39 +2476,42 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>22</v>
+        <v>8.9</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2451,65 +2519,85 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>22</v>
+        <v>8.9</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K54" s="2" t="n">
-        <v>22</v>
+        <v>8.9</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>残酷射手</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2517,39 +2605,42 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1.7</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2557,65 +2648,85 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1.7</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K57" s="2" t="n">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>泰森</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2623,39 +2734,42 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>18.4</v>
+        <v>12.7</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>8.5</v>
+        <v>-1.2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2663,39 +2777,42 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="F59" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G59" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>10</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>18.4</v>
+        <v>12.7</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>8.5</v>
+        <v>-1.2</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>垃圾刺客</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2703,39 +2820,42 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>18.4</v>
+        <v>12.7</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>8.5</v>
+        <v>-1.2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2743,13 +2863,13 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
@@ -2759,14 +2879,14 @@
         <v>1.1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>24.2</v>
+        <v>14.7</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-8.5</v>
+        <v>-5.6</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -2775,7 +2895,10 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2783,30 +2906,30 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>24.2</v>
+        <v>14.7</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>-8.5</v>
+        <v>-5.6</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -2815,7 +2938,10 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2823,30 +2949,30 @@
         <v>19</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>24.2</v>
+        <v>14.7</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>-8.5</v>
+        <v>-5.6</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -2855,7 +2981,10 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2873,16 +3002,16 @@
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>15.2</v>
+        <v>9.5</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-5</v>
+        <v>4.5</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -2895,7 +3024,10 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2903,30 +3035,30 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>15.2</v>
+        <v>9.5</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>-5</v>
+        <v>4.5</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -2935,7 +3067,10 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2943,30 +3078,30 @@
         <v>20</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>15.2</v>
+        <v>9.5</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>-5</v>
+        <v>4.5</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -2975,7 +3110,10 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/新数据生成/关卡表/10030.xlsx
+++ b/新数据生成/关卡表/10030.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>25.5</v>
+        <v>14.8</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5.1</v>
+        <v>-8.5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>粉蝾螈</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -756,30 +756,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2004</v>
+        <v>2037</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>25.5</v>
+        <v>14.8</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.1</v>
+        <v>-8.5</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -805,10 +805,10 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="n">
-        <v>25.5</v>
+        <v>14.8</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.1</v>
+        <v>-8.5</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -826,30 +826,30 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2002</v>
+        <v>2031</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英黄石怪</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -869,30 +869,30 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2006</v>
+        <v>2029</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>精英粉蝾螈</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -912,30 +912,30 @@
         <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="F12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精英粉蝙蝠</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -955,42 +955,42 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2001</v>
+        <v>2035</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>12.2</v>
+        <v>20.6</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-0.3</v>
+        <v>-7.1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿蝾螈</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1001,82 +1001,66 @@
         <v>2003</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K14" s="2" t="n">
-        <v>12.2</v>
+        <v>20.6</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-0.3</v>
+        <v>-7.1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄树怪</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="n">
-        <v>12.2</v>
+        <v>20.6</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>残酷射手</t>
-        </is>
-      </c>
+        <v>-7.1</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>3.4</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1084,30 +1068,30 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>14.3</v>
+        <v>19.1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英黄电兔</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1116,10 +1100,10 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1127,30 +1111,30 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>14.3</v>
+        <v>19.1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>垃圾刺客</t>
+          <t>精英绿皮怪1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1159,53 +1143,37 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>2005</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="n">
-        <v>14.3</v>
+        <v>19.1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>刘易斯</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1213,30 +1181,30 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2001</v>
+        <v>2037</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.2</v>
+        <v>1.4</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1245,10 +1213,10 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1256,30 +1224,30 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.2</v>
+        <v>1.4</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1288,53 +1256,37 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>泰森</t>
-        </is>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1342,30 +1294,30 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>21.1</v>
+        <v>18.2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英黄电兔</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1374,10 +1326,10 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1385,30 +1337,30 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2006</v>
+        <v>2044</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>21.1</v>
+        <v>18.2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>精英绿花</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -1417,53 +1369,37 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="n">
-        <v>21.1</v>
+        <v>18.2</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1471,42 +1407,42 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2001</v>
+        <v>2035</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>12</v>
+        <v>24.4</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-1.4</v>
+        <v>-5.4</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿蝾螈</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1517,39 +1453,39 @@
         <v>2004</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>12</v>
+        <v>24.4</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-1.4</v>
+        <v>-5.4</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1557,42 +1493,42 @@
         <v>7</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2003</v>
+        <v>2028</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>12</v>
+        <v>24.4</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>-1.4</v>
+        <v>-5.4</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1600,30 +1536,30 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>19.2</v>
+        <v>22.5</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英岩石龟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1632,10 +1568,10 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1643,30 +1579,30 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>19.2</v>
+        <v>22.5</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>精英黄鹿角</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -1675,10 +1611,10 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1686,30 +1622,30 @@
         <v>8</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2005</v>
+        <v>2030</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>19.2</v>
+        <v>22.5</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精英黄蝾螈</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -1718,10 +1654,10 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1729,30 +1665,30 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2003</v>
+        <v>2039</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-3.6</v>
+        <v>-5</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -1761,10 +1697,10 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1772,30 +1708,30 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>-3.6</v>
+        <v>-5</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -1804,37 +1740,53 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K33" s="2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>绿蘑菇</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1842,42 +1794,42 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2001</v>
+        <v>2039</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>17.7</v>
+        <v>11.9</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>4.2</v>
+        <v>-7.2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1885,69 +1837,89 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>17.7</v>
+        <v>11.9</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>4.2</v>
+        <v>-7.2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>黄树怪</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>3905</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>7146</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K36" s="2" t="n">
-        <v>17.7</v>
+        <v>11.9</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+        <v>-7.2</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>岩石巨人1</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1955,42 +1927,42 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2004</v>
+        <v>2027</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>26.9</v>
+        <v>14.1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1998,42 +1970,42 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2003</v>
+        <v>2028</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>26.9</v>
+        <v>14.1</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>-8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2047,20 +2019,20 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="n">
-        <v>26.9</v>
+        <v>14.1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2068,10 +2040,10 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2002</v>
+        <v>2045</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>1</v>
@@ -2084,14 +2056,14 @@
         <v>1.2</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>21.5</v>
+        <v>20.3</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英绿螃蟹</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2100,10 +2072,10 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2111,30 +2083,30 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2006</v>
+        <v>2046</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>21.5</v>
+        <v>20.3</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>精英绿蘑菇</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2143,53 +2115,37 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="n">
-        <v>21.5</v>
+        <v>20.3</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O42" s="2" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2197,30 +2153,30 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2001</v>
+        <v>2036</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-1.5</v>
+        <v>-0.4</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿兔子</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2229,10 +2185,10 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2240,30 +2196,30 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>-1.5</v>
+        <v>-0.4</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>粉蝾螈</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2272,10 +2228,10 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2283,30 +2239,30 @@
         <v>13</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2004</v>
+        <v>2040</v>
       </c>
       <c r="F45" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G45" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>-1.5</v>
+        <v>-0.4</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2315,10 +2271,10 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2326,30 +2282,30 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2003</v>
+        <v>2028</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>24.6</v>
+        <v>22.2</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-4</v>
+        <v>-6.4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2358,10 +2314,10 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2369,30 +2325,30 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2008</v>
+        <v>2035</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>24.6</v>
+        <v>22.2</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>-4</v>
+        <v>-6.4</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>绿蝾螈</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2401,37 +2357,53 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" s="2" t="n">
-        <v>24.6</v>
+        <v>22.2</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+        <v>-6.4</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>黄鹿角</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2439,42 +2411,42 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2004</v>
+        <v>2025</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>20.1</v>
+        <v>17.2</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>-8</v>
+        <v>7.9</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -2482,42 +2454,42 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2003</v>
+        <v>2038</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>20.1</v>
+        <v>17.2</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>-8</v>
+        <v>7.9</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2525,42 +2497,42 @@
         <v>15</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>20.1</v>
+        <v>17.2</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>-8</v>
+        <v>7.9</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2568,42 +2540,42 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2003</v>
+        <v>2040</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>12</v>
+        <v>22.7</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3.2</v>
+        <v>-5.9</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2611,42 +2583,42 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J53" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J53" s="2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K53" s="2" t="n">
-        <v>12</v>
+        <v>22.7</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>3.2</v>
+        <v>-5.9</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2654,42 +2626,42 @@
         <v>16</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>12</v>
+        <v>22.7</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3.2</v>
+        <v>-5.9</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2697,30 +2669,30 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2004</v>
+        <v>2025</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -2729,10 +2701,10 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2740,30 +2712,30 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -2772,10 +2744,10 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2783,30 +2755,30 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2003</v>
+        <v>2028</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -2815,10 +2787,10 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2826,30 +2798,30 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2004</v>
+        <v>2037</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>-5.5</v>
+        <v>-7.5</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -2858,10 +2830,10 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2869,30 +2841,30 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>-5.5</v>
+        <v>-7.5</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -2901,37 +2873,53 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="D60" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K60" s="2" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+        <v>-7.5</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>蜗牛</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2939,42 +2927,42 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>11</v>
+        <v>22.2</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-2.9</v>
+        <v>-10</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>粉蝾螈</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2982,42 +2970,42 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>11</v>
+        <v>22.2</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>-2.9</v>
+        <v>-10</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄鹿角</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -3031,20 +3019,20 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="n">
-        <v>11</v>
+        <v>22.2</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>-2.9</v>
+        <v>-10</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -3052,30 +3040,30 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2003</v>
+        <v>2038</v>
       </c>
       <c r="F64" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G64" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>24.4</v>
+        <v>17.7</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-7.1</v>
+        <v>-3.5</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3084,10 +3072,10 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -3095,13 +3083,13 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G65" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
@@ -3111,14 +3099,14 @@
         <v>1.1</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>24.4</v>
+        <v>17.7</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>-7.1</v>
+        <v>-3.5</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3127,10 +3115,10 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -3144,10 +3132,10 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="n">
-        <v>24.4</v>
+        <v>17.7</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>-7.1</v>
+        <v>-3.5</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
@@ -3157,7 +3145,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/新数据生成/关卡表/10030.xlsx
+++ b/新数据生成/关卡表/10030.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>14.8</v>
+        <v>22.7</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-8.5</v>
+        <v>-9.5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>粉蝾螈</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -756,30 +756,28 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2037</v>
+        <v>2028</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>14.8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="n">
-        <v>-8.5</v>
+        <v>-9.5</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>绿蝙蝠</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -804,11 +802,9 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="n">
-        <v>-8.5</v>
+        <v>-9.5</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
@@ -826,30 +822,30 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2031</v>
+        <v>2009</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>20.6</v>
+        <v>30.1</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>精英黄石怪</t>
+          <t>精英黄电兔</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -868,41 +864,23 @@
       <c r="D11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>2029</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>精英粉蝾螈</t>
-        </is>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="n">
         <v>2</v>
       </c>
@@ -911,41 +889,23 @@
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>精英粉蝙蝠</t>
-        </is>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="n">
         <v>2</v>
       </c>
@@ -955,30 +915,30 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2035</v>
+        <v>2026</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>20.6</v>
+        <v>24.1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-7.1</v>
+        <v>-8.9</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>绿蝾螈</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -998,13 +958,13 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
@@ -1013,15 +973,13 @@
       <c r="J14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="n">
-        <v>-7.1</v>
+        <v>-8.9</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>黄树怪</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1046,11 +1004,9 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="n">
-        <v>-7.1</v>
+        <v>-8.9</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
@@ -1071,23 +1027,23 @@
         <v>2009</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>19.1</v>
+        <v>30.8</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1110,41 +1066,23 @@
       <c r="D17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>精英绿皮怪1</t>
-        </is>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O17" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="n">
         <v>2</v>
       </c>
@@ -1159,11 +1097,9 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
@@ -1181,35 +1117,35 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2037</v>
+        <v>2006</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>23.6</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.4</v>
+        <v>-6.8</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>绿蝙蝠</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
@@ -1224,35 +1160,33 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2026</v>
+        <v>2007</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="n">
-        <v>1.4</v>
+        <v>-6.8</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
@@ -1266,25 +1200,39 @@
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="I21" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+        <v>-6.8</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>紫蝙蝠</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P21" s="2" t="n">
         <v>2</v>
       </c>
@@ -1297,23 +1245,23 @@
         <v>2009</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>18.2</v>
+        <v>29.2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1336,41 +1284,23 @@
       <c r="D23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>2044</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>精英绿花</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O23" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="n">
         <v>2</v>
       </c>
@@ -1385,11 +1315,9 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
@@ -1407,35 +1335,35 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2035</v>
+        <v>2002</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>24.4</v>
+        <v>10.1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-5.4</v>
+        <v>0.2</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>绿蝾螈</t>
+          <t>黄电兔</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
@@ -1450,35 +1378,33 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="n">
-        <v>-5.4</v>
+        <v>0.2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
@@ -1492,41 +1418,23 @@
       <c r="D27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>黄犀牛</t>
-        </is>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="n">
         <v>2</v>
       </c>
@@ -1536,30 +1444,30 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>22.5</v>
+        <v>29.8</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>6.3</v>
+        <v>2.6</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>精英岩石龟</t>
+          <t>精英黄电兔</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1578,41 +1486,23 @@
       <c r="D29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>精英黄鹿角</t>
-        </is>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O29" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="n">
         <v>2</v>
       </c>
@@ -1621,41 +1511,23 @@
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>2030</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>精英黄蝾螈</t>
-        </is>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="n">
         <v>2</v>
       </c>
@@ -1665,7 +1537,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2039</v>
+        <v>2002</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
@@ -1675,20 +1547,20 @@
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>8.4</v>
+        <v>10.4</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-5</v>
+        <v>-1.1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>绿螃蟹</t>
+          <t>黄电兔</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -1708,30 +1580,28 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>8.4</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="n">
-        <v>-5</v>
+        <v>-1.1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -1750,41 +1620,23 @@
       <c r="D33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>绿蘑菇</t>
-        </is>
-      </c>
+        <v>-1.1</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O33" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="n">
         <v>2</v>
       </c>
@@ -1794,35 +1646,35 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2039</v>
+        <v>2002</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>11.9</v>
+        <v>17.5</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>-7.2</v>
+        <v>6.3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>绿螃蟹</t>
+          <t>黄电兔</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
@@ -1837,35 +1689,33 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>12</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>11.9</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="n">
-        <v>-7.2</v>
+        <v>6.3</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>黄树怪</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
@@ -1879,45 +1729,23 @@
       <c r="D36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>7146</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>岩石巨人1</t>
-        </is>
-      </c>
+        <v>6.3</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>地狱</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="n">
         <v>2</v>
       </c>
@@ -1927,30 +1755,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>4.5</v>
+        <v>-4.4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>黄战士</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -1973,23 +1801,21 @@
         <v>2028</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>14.1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="n">
-        <v>4.5</v>
+        <v>-4.4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -2018,11 +1844,9 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="n">
-        <v>4.5</v>
+        <v>-4.4</v>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
@@ -2040,30 +1864,30 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2045</v>
+        <v>2009</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>20.3</v>
+        <v>31.3</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>精英绿螃蟹</t>
+          <t>精英黄电兔</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2082,41 +1906,23 @@
       <c r="D41" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>2046</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>精英绿蘑菇</t>
-        </is>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O41" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="n">
         <v>2</v>
       </c>
@@ -2131,11 +1937,9 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
@@ -2153,35 +1957,35 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2036</v>
+        <v>2007</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>6</v>
+        <v>19.1</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-0.4</v>
+        <v>-4.5</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>绿兔子</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O43" s="2" t="n">
@@ -2196,35 +2000,33 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K44" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="n">
-        <v>-0.4</v>
+        <v>-4.5</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>粉蝾螈</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O44" s="2" t="n">
@@ -2238,41 +2040,23 @@
       <c r="D45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>绿蘑菇</t>
-        </is>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="n">
         <v>2</v>
       </c>
@@ -2282,35 +2066,35 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2028</v>
+        <v>2009</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>22.2</v>
+        <v>28.4</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-6.4</v>
+        <v>-4.1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>精英黄电兔</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
@@ -2324,41 +2108,23 @@
       <c r="D47" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>2035</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>绿蝾螈</t>
-        </is>
-      </c>
+        <v>-4.1</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="n">
         <v>2</v>
       </c>
@@ -2367,41 +2133,23 @@
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>2001</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>黄鹿角</t>
-        </is>
-      </c>
+        <v>-4.1</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="n">
         <v>2</v>
       </c>
@@ -2411,35 +2159,35 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2025</v>
+        <v>2006</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>17.2</v>
+        <v>20.8</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>7.9</v>
+        <v>-6.2</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O49" s="2" t="n">
@@ -2454,35 +2202,33 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2038</v>
+        <v>2007</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K50" s="2" t="n">
-        <v>17.2</v>
-      </c>
+      <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="n">
-        <v>7.9</v>
+        <v>-6.2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>绿花</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O50" s="2" t="n">
@@ -2497,35 +2243,33 @@
         <v>15</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2007</v>
+        <v>2026</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>17.2</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="n">
-        <v>7.9</v>
+        <v>-6.2</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O51" s="2" t="n">
@@ -2540,35 +2284,35 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2040</v>
+        <v>2006</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>22.7</v>
+        <v>16.4</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-5.9</v>
+        <v>-0.3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>绿蘑菇</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O52" s="2" t="n">
@@ -2583,35 +2327,33 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>22.7</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="n">
-        <v>-5.9</v>
+        <v>-0.3</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O53" s="2" t="n">
@@ -2626,35 +2368,33 @@
         <v>16</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2007</v>
+        <v>2028</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K54" s="2" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="n">
-        <v>-5.9</v>
+        <v>-0.3</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O54" s="2" t="n">
@@ -2669,30 +2409,30 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>6.2</v>
+        <v>12.9</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>-1.9</v>
+        <v>-2.9</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -2712,30 +2452,28 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>9</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J56" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="n">
-        <v>-1.9</v>
+        <v>-2.9</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -2754,41 +2492,23 @@
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>黄犀牛</t>
-        </is>
-      </c>
+        <v>-2.9</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O57" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="n">
         <v>2</v>
       </c>
@@ -2798,10 +2518,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2037</v>
+        <v>2006</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>10</v>
@@ -2811,17 +2531,17 @@
         <v>0.6</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>-7.5</v>
+        <v>-5.9</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>绿蝙蝠</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -2841,10 +2561,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>9</v>
@@ -2854,17 +2574,15 @@
         <v>0.5</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>20.2</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="n">
-        <v>-7.5</v>
+        <v>-5.9</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -2883,41 +2601,23 @@
       <c r="D60" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>20.2</v>
-      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>蜗牛</t>
-        </is>
-      </c>
+        <v>-5.9</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O60" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="n">
         <v>2</v>
       </c>
@@ -2927,35 +2627,35 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2023</v>
+        <v>2002</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>22.2</v>
+        <v>11.5</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-10</v>
+        <v>2.7</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>粉蝾螈</t>
+          <t>黄电兔</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
@@ -2970,35 +2670,33 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>22.2</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="n">
-        <v>-10</v>
+        <v>2.7</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>黄鹿角</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O62" s="2" t="n">
@@ -3012,25 +2710,39 @@
       <c r="D63" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="I63" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>绿皮怪1</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P63" s="2" t="n">
         <v>2</v>
       </c>
@@ -3040,30 +2752,30 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2038</v>
+        <v>2028</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>17.7</v>
+        <v>14.6</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-3.5</v>
+        <v>-5.6</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>绿花</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3083,10 +2795,10 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>9</v>
@@ -3098,15 +2810,13 @@
       <c r="J65" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K65" s="2" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="n">
-        <v>-3.5</v>
+        <v>-5.6</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3125,25 +2835,39 @@
       <c r="D66" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="I66" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+        <v>-5.6</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>紫蝙蝠</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P66" s="2" t="n">
         <v>2</v>
       </c>

--- a/新数据生成/关卡表/10030.xlsx
+++ b/新数据生成/关卡表/10030.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-9.5</v>
+        <v>-3.9</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -759,21 +759,21 @@
         <v>2028</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="n">
-        <v>-9.5</v>
+        <v>-3.9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="n">
-        <v>-9.5</v>
+        <v>-3.9</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
@@ -822,35 +822,35 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>30.1</v>
+        <v>24.6</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2.2</v>
+        <v>-4.3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>精英黄电兔</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O10" s="2" t="n">
@@ -864,23 +864,39 @@
       <c r="D11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+        <v>-4.3</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>粉蝙蝠</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P11" s="2" t="n">
         <v>2</v>
       </c>
@@ -897,12 +913,12 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="n">
-        <v>2.2</v>
+        <v>-4.3</v>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
@@ -915,30 +931,30 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>24.1</v>
+        <v>26.9</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-8.9</v>
+        <v>-7.1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -958,28 +974,28 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2006</v>
+        <v>2028</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="n">
-        <v>-8.9</v>
+        <v>-7.1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1006,7 +1022,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="n">
-        <v>-8.9</v>
+        <v>-7.1</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
@@ -1024,35 +1040,35 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>30.8</v>
+        <v>21.1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5.7</v>
+        <v>-4.9</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>精英黄电兔</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
@@ -1066,23 +1082,39 @@
       <c r="D17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+        <v>-4.9</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>黄犀牛</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P17" s="2" t="n">
         <v>2</v>
       </c>
@@ -1091,23 +1123,39 @@
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+        <v>-4.9</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>绿皮怪1</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P18" s="2" t="n">
         <v>2</v>
       </c>
@@ -1117,30 +1165,30 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>23.6</v>
+        <v>25.6</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-6.8</v>
+        <v>-9.4</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1160,28 +1208,28 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="n">
-        <v>-6.8</v>
+        <v>-9.4</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1201,28 +1249,28 @@
         <v>5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="n">
-        <v>-6.8</v>
+        <v>-9.4</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -1242,35 +1290,35 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>29.2</v>
+        <v>20.2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2.5</v>
+        <v>-4.6</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>精英黄电兔</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
@@ -1284,23 +1332,39 @@
       <c r="D23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+        <v>-4.6</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>黄犀牛</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P23" s="2" t="n">
         <v>2</v>
       </c>
@@ -1317,12 +1381,12 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="n">
-        <v>2.5</v>
+        <v>-4.6</v>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -1335,35 +1399,35 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>10.1</v>
+        <v>24.4</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.2</v>
+        <v>-9.5</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>黄电兔</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
@@ -1378,33 +1442,33 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="n">
-        <v>0.2</v>
+        <v>-9.5</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
@@ -1418,23 +1482,39 @@
       <c r="D27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+        <v>-9.5</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>绿皮怪1</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr"/>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P27" s="2" t="n">
         <v>2</v>
       </c>
@@ -1444,35 +1524,35 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>29.8</v>
+        <v>16.6</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2.6</v>
+        <v>-4.5</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>精英黄电兔</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O28" s="2" t="n">
@@ -1486,23 +1566,39 @@
       <c r="D29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+        <v>-4.5</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>黄犀牛</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P29" s="2" t="n">
         <v>2</v>
       </c>
@@ -1511,23 +1607,39 @@
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+        <v>-4.5</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>绿皮怪1</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P30" s="2" t="n">
         <v>2</v>
       </c>
@@ -1537,35 +1649,35 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>10.4</v>
+        <v>25.7</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-1.1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>黄电兔</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
@@ -1580,33 +1692,33 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="n">
-        <v>-1.1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
@@ -1628,12 +1740,12 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="n">
-        <v>-1.1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -1646,30 +1758,30 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>黄电兔</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -1689,28 +1801,28 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2007</v>
+        <v>2028</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -1729,23 +1841,41 @@
       <c r="D36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="n">
+        <v>3025</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1687</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>黄石怪</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>地狱</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P36" s="2" t="n">
         <v>2</v>
       </c>
@@ -1755,30 +1885,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>12.1</v>
+        <v>15.1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-4.4</v>
+        <v>-4.3</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -1798,28 +1928,28 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2028</v>
+        <v>2004</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="n">
-        <v>-4.4</v>
+        <v>-4.3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -1838,23 +1968,39 @@
       <c r="D39" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+        <v>-4.3</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>绿皮怪1</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P39" s="2" t="n">
         <v>2</v>
       </c>
@@ -1864,30 +2010,30 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>31.3</v>
+        <v>18</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>精英黄电兔</t>
+          <t>精英岩石龟</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -1906,23 +2052,39 @@
       <c r="D41" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>精英绿蝾螈</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P41" s="2" t="n">
         <v>2</v>
       </c>
@@ -1931,23 +2093,39 @@
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>精英黄蝾螈</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P42" s="2" t="n">
         <v>2</v>
       </c>
@@ -1957,30 +2135,30 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>19.1</v>
+        <v>13.1</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-4.5</v>
+        <v>-10.3</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2000,28 +2178,28 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="n">
-        <v>-4.5</v>
+        <v>-10.3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2040,23 +2218,39 @@
       <c r="D45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+        <v>-10.3</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>绿皮怪1</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P45" s="2" t="n">
         <v>2</v>
       </c>
@@ -2066,30 +2260,30 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>28.4</v>
+        <v>16.5</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-4.1</v>
+        <v>5</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>精英黄电兔</t>
+          <t>精英岩石龟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2108,23 +2302,39 @@
       <c r="D47" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>精英黄蝾螈</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P47" s="2" t="n">
         <v>2</v>
       </c>
@@ -2133,23 +2343,39 @@
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>精英紫蝙蝠</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P48" s="2" t="n">
         <v>2</v>
       </c>
@@ -2159,30 +2385,30 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>20.8</v>
+        <v>15.3</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>-6.2</v>
+        <v>-9</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -2202,28 +2428,28 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="n">
-        <v>-6.2</v>
+        <v>-9</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -2243,28 +2469,28 @@
         <v>15</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="F51" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G51" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>8</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="n">
-        <v>-6.2</v>
+        <v>-9</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -2284,35 +2510,35 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>16.4</v>
+        <v>14.5</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-0.3</v>
+        <v>3.8</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>精英岩石龟</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O52" s="2" t="n">
@@ -2327,33 +2553,33 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2026</v>
+        <v>2041</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="n">
-        <v>-0.3</v>
+        <v>3.8</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>精英绿蝾螈</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O53" s="2" t="n">
@@ -2367,39 +2593,23 @@
       <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>黄犀牛</t>
-        </is>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="n">
         <v>2</v>
       </c>
@@ -2409,30 +2619,30 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>-2.9</v>
+        <v>-4.2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -2455,21 +2665,21 @@
         <v>2006</v>
       </c>
       <c r="F56" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G56" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>9</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="n">
-        <v>-2.9</v>
+        <v>-4.2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -2492,23 +2702,39 @@
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+        <v>-4.2</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>粉蝙蝠</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P57" s="2" t="n">
         <v>2</v>
       </c>
@@ -2518,35 +2744,35 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>21</v>
+        <v>19.7</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>-5.9</v>
+        <v>2.7</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>精英岩石龟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O58" s="2" t="n">
@@ -2561,33 +2787,33 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2026</v>
+        <v>2041</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="n">
-        <v>-5.9</v>
+        <v>2.7</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>精英绿蝾螈</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O59" s="2" t="n">
@@ -2609,12 +2835,12 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="n">
-        <v>-5.9</v>
+        <v>2.7</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr"/>
@@ -2627,35 +2853,35 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>11.5</v>
+        <v>16.8</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2.7</v>
+        <v>-9.1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>黄电兔</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
@@ -2670,33 +2896,33 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2007</v>
+        <v>2028</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="n">
-        <v>2.7</v>
+        <v>-9.1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O62" s="2" t="n">
@@ -2710,39 +2936,23 @@
       <c r="D63" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>绿皮怪1</t>
-        </is>
-      </c>
+        <v>-9.1</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="n">
         <v>2</v>
       </c>
@@ -2752,35 +2962,35 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2028</v>
+        <v>2012</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>14.6</v>
+        <v>12.7</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-5.6</v>
+        <v>9.9</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>精英岩石龟</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
@@ -2795,33 +3005,33 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="n">
-        <v>-5.6</v>
+        <v>9.9</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>精英蜗牛</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O65" s="2" t="n">
@@ -2836,33 +3046,33 @@
         <v>20</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="n">
-        <v>-5.6</v>
+        <v>9.9</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>精英紫蝙蝠</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O66" s="2" t="n">

--- a/新数据生成/关卡表/10030.xlsx
+++ b/新数据生成/关卡表/10030.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>23.3</v>
+        <v>28</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-3.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -755,39 +755,21 @@
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>黄犀牛</t>
-        </is>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="n">
         <v>2</v>
       </c>
@@ -803,9 +785,7 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="n">
-        <v>-3.9</v>
-      </c>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -822,30 +802,30 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>24.6</v>
+        <v>20.9</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4.3</v>
+        <v>-6.7</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -865,13 +845,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
@@ -881,12 +861,10 @@
         <v>1.2</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n">
-        <v>-4.3</v>
-      </c>
+      <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -912,9 +890,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="n">
-        <v>-4.3</v>
-      </c>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -931,30 +907,30 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-7.1</v>
+        <v>-10.9</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -973,39 +949,21 @@
       <c r="D14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>黄犀牛</t>
-        </is>
-      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="n">
         <v>2</v>
       </c>
@@ -1021,9 +979,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="n">
-        <v>-7.1</v>
-      </c>
+      <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1040,30 +996,30 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.9</v>
+        <v>-8</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1083,28 +1039,26 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2028</v>
+        <v>2007</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="n">
-        <v>-4.9</v>
-      </c>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1123,39 +1077,21 @@
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>绿皮怪1</t>
-        </is>
-      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="n">
         <v>2</v>
       </c>
@@ -1165,30 +1101,30 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>25.6</v>
+        <v>22.5</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-9.4</v>
+        <v>-10.2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1208,28 +1144,26 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="n">
-        <v>-9.4</v>
-      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1248,39 +1182,21 @@
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>绿皮怪1</t>
-        </is>
-      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="n">
         <v>2</v>
       </c>
@@ -1290,35 +1206,35 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>20.2</v>
+        <v>27.2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>-4.6</v>
+        <v>-12.3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>精英岩石龟</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
@@ -1332,39 +1248,21 @@
       <c r="D23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>黄犀牛</t>
-        </is>
-      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="n">
         <v>2</v>
       </c>
@@ -1380,13 +1278,11 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="n">
-        <v>-4.6</v>
-      </c>
+      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -1399,35 +1295,35 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>24.4</v>
+        <v>17.5</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-9.5</v>
+        <v>-11</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
@@ -1442,33 +1338,31 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="n">
-        <v>-9.5</v>
-      </c>
+      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
@@ -1482,39 +1376,21 @@
       <c r="D27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>绿皮怪1</t>
-        </is>
-      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="n">
         <v>2</v>
       </c>
@@ -1524,13 +1400,13 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
@@ -1540,19 +1416,19 @@
         <v>1.2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-4.5</v>
+        <v>-10.4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>精英岩石龟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O28" s="2" t="n">
@@ -1567,33 +1443,31 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2028</v>
+        <v>2011</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="n">
-        <v>-4.5</v>
-      </c>
+      <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>精英粉蝙蝠</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O29" s="2" t="n">
@@ -1607,39 +1481,21 @@
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>绿皮怪1</t>
-        </is>
-      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="n">
         <v>2</v>
       </c>
@@ -1649,35 +1505,35 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>25.7</v>
+        <v>15.9</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-9.699999999999999</v>
+        <v>-12.9</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
@@ -1692,13 +1548,13 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
@@ -1708,17 +1564,15 @@
         <v>1.1</v>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="n">
-        <v>-9.699999999999999</v>
-      </c>
+      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
@@ -1739,13 +1593,11 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="n">
-        <v>-9.699999999999999</v>
-      </c>
+      <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -1757,16 +1609,20 @@
       <c r="D34" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>2025</v>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>3910</t>
+        </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>5472</v>
+      </c>
       <c r="I34" s="2" t="n">
         <v>0.5</v>
       </c>
@@ -1774,19 +1630,19 @@
         <v>1.1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>9.6</v>
+        <v>28.5</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>7</v>
+        <v>-16.8</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>浪哩个浪</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
@@ -1800,39 +1656,21 @@
       <c r="D35" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>黄犀牛</t>
-        </is>
-      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="n">
         <v>2</v>
       </c>
@@ -1841,41 +1679,21 @@
       <c r="D36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>3025</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>1687</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>黄石怪</t>
-        </is>
-      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="n">
         <v>2</v>
       </c>
@@ -1885,35 +1703,35 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>15.1</v>
+        <v>16.1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-4.3</v>
+        <v>-15</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O37" s="2" t="n">
@@ -1928,33 +1746,31 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="n">
-        <v>-4.3</v>
-      </c>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O38" s="2" t="n">
@@ -1969,33 +1785,31 @@
         <v>11</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="n">
-        <v>-4.3</v>
-      </c>
+      <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>黄树怪</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O39" s="2" t="n">
@@ -2013,23 +1827,23 @@
         <v>2012</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3.6</v>
+        <v>-14.4</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2053,28 +1867,26 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2041</v>
+        <v>2030</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>精英绿蝾螈</t>
+          <t>精英黄蝾螈</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2093,39 +1905,21 @@
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>2030</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>精英黄蝾螈</t>
-        </is>
-      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O42" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="n">
         <v>2</v>
       </c>
@@ -2135,30 +1929,30 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>13.1</v>
+        <v>15.2</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-10.3</v>
+        <v>-17</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2178,28 +1972,26 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2028</v>
+        <v>2007</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="n">
-        <v>-10.3</v>
-      </c>
+      <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2219,28 +2011,26 @@
         <v>13</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="n">
-        <v>-10.3</v>
-      </c>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>黄树怪</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2266,20 +2056,20 @@
         <v>4</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>5</v>
+        <v>-16.8</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -2306,22 +2096,20 @@
         <v>2030</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
           <t>精英黄蝾螈</t>
@@ -2343,39 +2131,21 @@
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>2032</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>精英紫蝙蝠</t>
-        </is>
-      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O48" s="2" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="n">
         <v>2</v>
       </c>
@@ -2385,30 +2155,30 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>-9</v>
+        <v>-19</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -2428,28 +2198,26 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -2469,28 +2237,26 @@
         <v>15</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2006</v>
+        <v>2026</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -2516,7 +2282,7 @@
         <v>4</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
@@ -2526,10 +2292,10 @@
         <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>14.5</v>
+        <v>15.2</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3.8</v>
+        <v>-19.2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -2553,28 +2319,26 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2041</v>
+        <v>2011</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>精英绿蝾螈</t>
+          <t>精英粉蝙蝠</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -2593,23 +2357,37 @@
       <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>精英黄树怪</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P54" s="2" t="n">
         <v>2</v>
       </c>
@@ -2619,13 +2397,13 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
@@ -2635,14 +2413,14 @@
         <v>1.1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>13.7</v>
+        <v>16.2</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>-4.2</v>
+        <v>-20</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -2662,13 +2440,13 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
@@ -2678,12 +2456,10 @@
         <v>1.1</v>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="n">
-        <v>-4.2</v>
-      </c>
+      <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>黄树怪</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -2703,28 +2479,26 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="n">
-        <v>-4.2</v>
-      </c>
+      <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -2747,23 +2521,23 @@
         <v>2012</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>19.7</v>
+        <v>15.7</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2.7</v>
+        <v>-20.1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -2787,28 +2561,26 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>精英绿蝾螈</t>
+          <t>精英黄树怪</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -2834,9 +2606,7 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -2853,30 +2623,30 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-9.1</v>
+        <v>-22</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -2896,28 +2666,26 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2028</v>
+        <v>2007</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="n">
-        <v>-9.1</v>
-      </c>
+      <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -2936,23 +2704,37 @@
       <c r="D63" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>紫蝙蝠</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="P63" s="2" t="n">
         <v>2</v>
       </c>
@@ -2962,26 +2744,28 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2012</v>
+        <v>3012</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>5472</v>
+      </c>
       <c r="I64" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>12.7</v>
+        <v>28.4</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>9.9</v>
+        <v>-24</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -2990,7 +2774,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
@@ -3004,39 +2788,21 @@
       <c r="D65" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>精英蜗牛</t>
-        </is>
-      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>地狱</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="n">
         <v>2</v>
       </c>
@@ -3045,39 +2811,21 @@
       <c r="D66" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>2032</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>精英紫蝙蝠</t>
-        </is>
-      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>4.3</v>
-      </c>
+          <t>地狱</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="n">
         <v>2</v>
       </c>
